--- a/output_data/charts/crashSeverityByType-Morrow.xlsx
+++ b/output_data/charts/crashSeverityByType-Morrow.xlsx
@@ -34,46 +34,46 @@
     <t>Angle</t>
   </si>
   <si>
+    <t>Head On</t>
+  </si>
+  <si>
     <t>Rear End</t>
   </si>
   <si>
+    <t>Sideswipe - Passing</t>
+  </si>
+  <si>
     <t>Parked Vehicle</t>
   </si>
   <si>
+    <t>Animal</t>
+  </si>
+  <si>
     <t>Pedestrian</t>
   </si>
   <si>
-    <t>Sideswipe - Passing</t>
-  </si>
-  <si>
-    <t>Animal</t>
-  </si>
-  <si>
-    <t>Head On</t>
+    <t>Overturning</t>
   </si>
   <si>
     <t>Left Turn</t>
   </si>
   <si>
-    <t>Overturning</t>
-  </si>
-  <si>
     <t>Other Object</t>
   </si>
   <si>
+    <t>Pedalcycles</t>
+  </si>
+  <si>
+    <t>Other Non-Collision</t>
+  </si>
+  <si>
+    <t>Right Turn</t>
+  </si>
+  <si>
+    <t>Sideswipe - Meeting</t>
+  </si>
+  <si>
     <t>Backing</t>
-  </si>
-  <si>
-    <t>Other Non-Collision</t>
-  </si>
-  <si>
-    <t>Pedalcycles</t>
-  </si>
-  <si>
-    <t>Right Turn</t>
-  </si>
-  <si>
-    <t>Sideswipe - Meeting</t>
   </si>
   <si>
     <t>Unknown</t>
@@ -219,46 +219,46 @@
                   <c:v>Angle</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>Head On</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>Rear End</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
+                  <c:v>Sideswipe - Passing</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>Parked Vehicle</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Pedestrian</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Sideswipe - Passing</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Animal</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Head On</c:v>
+                  <c:v>Pedestrian</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>Overturning</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>Left Turn</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Overturning</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>Other Object</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>Backing</c:v>
+                  <c:v>Pedalcycles</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>Other Non-Collision</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>Pedalcycles</c:v>
+                  <c:v>Right Turn</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>Right Turn</c:v>
+                  <c:v>Sideswipe - Meeting</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>Sideswipe - Meeting</c:v>
+                  <c:v>Backing</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>Unknown</c:v>
@@ -273,34 +273,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>35.71428571428572</c:v>
+                  <c:v>24.24242424242424</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>14.28571428571428</c:v>
+                  <c:v>18.18181818181818</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14.28571428571428</c:v>
+                  <c:v>18.18181818181818</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.142857142857142</c:v>
+                  <c:v>15.15151515151515</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.142857142857142</c:v>
+                  <c:v>6.060606060606061</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7.142857142857142</c:v>
+                  <c:v>6.060606060606061</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.571428571428571</c:v>
+                  <c:v>3.03030303030303</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.571428571428571</c:v>
+                  <c:v>3.03030303030303</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.571428571428571</c:v>
+                  <c:v>3.03030303030303</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.571428571428571</c:v>
+                  <c:v>3.03030303030303</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -361,46 +361,46 @@
                   <c:v>Angle</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>Head On</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>Rear End</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
+                  <c:v>Sideswipe - Passing</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>Parked Vehicle</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Pedestrian</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Sideswipe - Passing</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Animal</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Head On</c:v>
+                  <c:v>Pedestrian</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>Overturning</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>Left Turn</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Overturning</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>Other Object</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>Backing</c:v>
+                  <c:v>Pedalcycles</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>Other Non-Collision</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>Pedalcycles</c:v>
+                  <c:v>Right Turn</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>Right Turn</c:v>
+                  <c:v>Sideswipe - Meeting</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>Sideswipe - Meeting</c:v>
+                  <c:v>Backing</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>Unknown</c:v>
@@ -415,49 +415,49 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>33.84615384615385</c:v>
+                  <c:v>35.9375</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15.38461538461539</c:v>
+                  <c:v>17.96875</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.461538461538462</c:v>
+                  <c:v>9.375</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>8.59375</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.90625</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>6.923076923076923</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>4.615384615384616</c:v>
-                </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.538461538461539</c:v>
+                  <c:v>1.5625</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.461538461538462</c:v>
+                  <c:v>7.03125</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.384615384615385</c:v>
+                  <c:v>10.9375</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>11.53846153846154</c:v>
+                  <c:v>3.125</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>0.78125</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.538461538461539</c:v>
+                  <c:v>0.78125</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.307692307692308</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
@@ -503,46 +503,46 @@
                   <c:v>Angle</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>Head On</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>Rear End</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
+                  <c:v>Sideswipe - Passing</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>Parked Vehicle</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Pedestrian</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Sideswipe - Passing</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Animal</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Head On</c:v>
+                  <c:v>Pedestrian</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>Overturning</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>Left Turn</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Overturning</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>Other Object</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>Backing</c:v>
+                  <c:v>Pedalcycles</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>Other Non-Collision</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>Pedalcycles</c:v>
+                  <c:v>Right Turn</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>Right Turn</c:v>
+                  <c:v>Sideswipe - Meeting</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>Sideswipe - Meeting</c:v>
+                  <c:v>Backing</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>Unknown</c:v>
@@ -557,55 +557,55 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>30.89467723669309</c:v>
+                  <c:v>29.95337995337995</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.561721404303512</c:v>
+                  <c:v>9.393939393939393</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.32502831257078</c:v>
+                  <c:v>2.261072261072261</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.223103057757644</c:v>
+                  <c:v>10.76923076923077</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.4077010192525481</c:v>
+                  <c:v>10.41958041958042</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>10.37372593431484</c:v>
+                  <c:v>1.421911421911422</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>21.17780294450736</c:v>
+                  <c:v>21.60839160839161</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.106455266138165</c:v>
+                  <c:v>0.5128205128205128</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.507361268403171</c:v>
+                  <c:v>1.794871794871795</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.7440543601359</c:v>
+                  <c:v>4.522144522144522</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.6795016987542469</c:v>
+                  <c:v>0.6293706293706294</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.106455266138165</c:v>
+                  <c:v>0.1165501165501165</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.287655719139298</c:v>
+                  <c:v>2.307692307692308</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.1812004530011325</c:v>
+                  <c:v>1.002331002331002</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.109852774631937</c:v>
+                  <c:v>0.04662004662004662</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.04530011325028312</c:v>
+                  <c:v>1.981351981351981</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.268403171007928</c:v>
+                  <c:v>1.258741258741259</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1061,13 +1061,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>35.71428571428572</v>
+        <v>24.24242424242424</v>
       </c>
       <c r="C2" s="2">
-        <v>33.84615384615385</v>
+        <v>35.9375</v>
       </c>
       <c r="D2" s="2">
-        <v>30.89467723669309</v>
+        <v>29.95337995337995</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1075,13 +1075,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2">
-        <v>14.28571428571428</v>
+        <v>18.18181818181818</v>
       </c>
       <c r="C3" s="2">
-        <v>15.38461538461539</v>
+        <v>17.96875</v>
       </c>
       <c r="D3" s="2">
-        <v>8.561721404303512</v>
+        <v>9.393939393939393</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1089,13 +1089,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2">
-        <v>14.28571428571428</v>
+        <v>18.18181818181818</v>
       </c>
       <c r="C4" s="2">
-        <v>8.461538461538462</v>
+        <v>9.375</v>
       </c>
       <c r="D4" s="2">
-        <v>11.32502831257078</v>
+        <v>2.261072261072261</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1103,13 +1103,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2">
-        <v>7.142857142857142</v>
+        <v>15.15151515151515</v>
       </c>
       <c r="C5" s="2">
-        <v>0</v>
+        <v>8.59375</v>
       </c>
       <c r="D5" s="2">
-        <v>1.223103057757644</v>
+        <v>10.76923076923077</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1117,13 +1117,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2">
-        <v>7.142857142857142</v>
+        <v>6.060606060606061</v>
       </c>
       <c r="C6" s="2">
-        <v>6.923076923076923</v>
+        <v>3.90625</v>
       </c>
       <c r="D6" s="2">
-        <v>0.4077010192525481</v>
+        <v>10.41958041958042</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1131,13 +1131,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2">
-        <v>7.142857142857142</v>
+        <v>6.060606060606061</v>
       </c>
       <c r="C7" s="2">
-        <v>4.615384615384616</v>
+        <v>0</v>
       </c>
       <c r="D7" s="2">
-        <v>10.37372593431484</v>
+        <v>1.421911421911422</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1145,13 +1145,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2">
-        <v>3.571428571428571</v>
+        <v>3.03030303030303</v>
       </c>
       <c r="C8" s="2">
-        <v>1.538461538461539</v>
+        <v>1.5625</v>
       </c>
       <c r="D8" s="2">
-        <v>21.17780294450736</v>
+        <v>21.60839160839161</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1159,13 +1159,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="2">
-        <v>3.571428571428571</v>
+        <v>3.03030303030303</v>
       </c>
       <c r="C9" s="2">
-        <v>8.461538461538462</v>
+        <v>7.03125</v>
       </c>
       <c r="D9" s="2">
-        <v>2.106455266138165</v>
+        <v>0.5128205128205128</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1173,13 +1173,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2">
-        <v>3.571428571428571</v>
+        <v>3.03030303030303</v>
       </c>
       <c r="C10" s="2">
-        <v>5.384615384615385</v>
+        <v>10.9375</v>
       </c>
       <c r="D10" s="2">
-        <v>4.507361268403171</v>
+        <v>1.794871794871795</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1187,13 +1187,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="2">
-        <v>3.571428571428571</v>
+        <v>3.03030303030303</v>
       </c>
       <c r="C11" s="2">
-        <v>11.53846153846154</v>
+        <v>3.125</v>
       </c>
       <c r="D11" s="2">
-        <v>1.7440543601359</v>
+        <v>4.522144522144522</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="2">
-        <v>0.6795016987542469</v>
+        <v>0.6293706293706294</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1218,10 +1218,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="2">
-        <v>0</v>
+        <v>0.78125</v>
       </c>
       <c r="D13" s="2">
-        <v>2.106455266138165</v>
+        <v>0.1165501165501165</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="2">
-        <v>2.287655719139298</v>
+        <v>2.307692307692308</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1246,10 +1246,10 @@
         <v>0</v>
       </c>
       <c r="C15" s="2">
-        <v>1.538461538461539</v>
+        <v>0.78125</v>
       </c>
       <c r="D15" s="2">
-        <v>0.1812004530011325</v>
+        <v>1.002331002331002</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1260,10 +1260,10 @@
         <v>0</v>
       </c>
       <c r="C16" s="2">
-        <v>2.307692307692308</v>
+        <v>0</v>
       </c>
       <c r="D16" s="2">
-        <v>1.109852774631937</v>
+        <v>0.04662004662004662</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1277,7 +1277,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="2">
-        <v>0.04530011325028312</v>
+        <v>1.981351981351981</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="2">
-        <v>1.268403171007928</v>
+        <v>1.258741258741259</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/crashSeverityByType-Morrow.xlsx
+++ b/output_data/charts/crashSeverityByType-Morrow.xlsx
@@ -83,8 +83,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode=""/>
+    <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -141,7 +142,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -173,7 +174,7 @@
               <a:rPr lang="en-US" sz="1400" baseline="0">
                 <a:latin typeface="Arial"/>
               </a:rPr>
-              <a:t>Crash Severity by Type of Crash - Morrow County</a:t>
+              <a:t>Crash Severity by Type of Crash, Morrow County, 2020-2024</a:t>
             </a:r>
           </a:p>
         </c:rich>
